--- a/archive/2026/2026-10-12.xlsx
+++ b/archive/2026/2026-10-12.xlsx
@@ -11776,22 +11776,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>00969B</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>松上</t>
+          <t>元大零息超長美債</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
         <v>553</v>
       </c>
       <c r="E38" t="n">
-        <v>26.15</v>
+        <v>7.46</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>2.35</v>
+        <v>0.23</v>
       </c>
       <c r="H38" t="n">
         <v>35</v>
@@ -11822,22 +11822,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>00969B</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>元大零息超長美債</t>
+          <t>松上</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
         <v>553</v>
       </c>
       <c r="E39" t="n">
-        <v>7.46</v>
+        <v>26.15</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.23</v>
+        <v>2.35</v>
       </c>
       <c r="H39" t="n">
         <v>36</v>
